--- a/data/trans_dic/IP22_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP22_R-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,86; 34,51</t>
+          <t>16,22; 34,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,87; 40,97</t>
+          <t>21,38; 40,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,25; 47,56</t>
+          <t>27,66; 47,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,56; 51,44</t>
+          <t>23,87; 50,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,76; 39,17</t>
+          <t>21,07; 40,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,06; 56,6</t>
+          <t>35,18; 56,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,18; 43,31</t>
+          <t>24,31; 44,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,97; 35,36</t>
+          <t>17,5; 36,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,69; 33,93</t>
+          <t>21,51; 35,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,24; 45,09</t>
+          <t>31,39; 46,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,51; 42,62</t>
+          <t>28,12; 42,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,04; 39,81</t>
+          <t>23,24; 39,71</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,95; 26,97</t>
+          <t>13,76; 26,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,22; 38,36</t>
+          <t>25,09; 40,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,61; 34,7</t>
+          <t>21,63; 34,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,71; 20,44</t>
+          <t>5,38; 20,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,31; 31,87</t>
+          <t>18,15; 31,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,75; 42,74</t>
+          <t>28,6; 44,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,38; 32,65</t>
+          <t>18,73; 33,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 18,93</t>
+          <t>7,51; 18,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,95; 27,22</t>
+          <t>17,94; 27,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,84; 39,1</t>
+          <t>28,62; 39,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22,51; 31,93</t>
+          <t>22,3; 32,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,16; 16,87</t>
+          <t>8,41; 17,02</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,76; 31,51</t>
+          <t>14,9; 32,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,07; 40,44</t>
+          <t>22,54; 41,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,3; 16,28</t>
+          <t>4,28; 16,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,38; 31,71</t>
+          <t>14,77; 31,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,08; 32,16</t>
+          <t>16,2; 32,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,25; 41,94</t>
+          <t>23,21; 41,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 10,52</t>
+          <t>1,03; 9,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 20,86</t>
+          <t>7,38; 20,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,93; 28,95</t>
+          <t>17,16; 29,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24,95; 38,29</t>
+          <t>24,88; 38,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,67; 10,61</t>
+          <t>3,83; 11,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,02; 22,83</t>
+          <t>12,43; 23,58</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,31; 29,59</t>
+          <t>14,88; 29,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,92; 33,77</t>
+          <t>17,57; 33,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,1; 34,26</t>
+          <t>18,11; 33,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,56; 27,45</t>
+          <t>9,8; 26,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,36; 29,98</t>
+          <t>14,45; 29,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,23; 38,99</t>
+          <t>21,14; 38,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,59; 42,96</t>
+          <t>26,05; 45,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,13; 31,18</t>
+          <t>9,24; 30,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,7; 27,55</t>
+          <t>16,46; 27,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,96; 33,53</t>
+          <t>22,18; 33,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23,98; 36,63</t>
+          <t>24,36; 36,26</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,84; 26,27</t>
+          <t>11,11; 25,05</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,63; 24,34</t>
+          <t>7,59; 23,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,16; 49,17</t>
+          <t>25,77; 48,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,77; 20,41</t>
+          <t>4,27; 20,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 15,31</t>
+          <t>1,3; 12,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,18; 24,49</t>
+          <t>6,13; 23,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,37; 38,41</t>
+          <t>16,68; 38,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,3</t>
+          <t>0,0; 9,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,52; 14,97</t>
+          <t>2,58; 15,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,49; 20,36</t>
+          <t>9,11; 20,38</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,51; 40,81</t>
+          <t>24,34; 40,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 12,32</t>
+          <t>2,96; 11,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 10,99</t>
+          <t>2,71; 11,17</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,08; 32,99</t>
+          <t>13,98; 32,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,42; 40,86</t>
+          <t>19,97; 39,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,71; 32,34</t>
+          <t>13,8; 33,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,97; 22,39</t>
+          <t>7,08; 22,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,7; 34,43</t>
+          <t>16,58; 33,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,25; 46,96</t>
+          <t>25,67; 47,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,81; 24,72</t>
+          <t>8,12; 24,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,07; 25,85</t>
+          <t>9,5; 25,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,08; 29,89</t>
+          <t>17,59; 30,69</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25,02; 40,81</t>
+          <t>25,74; 40,26</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13,37; 25,95</t>
+          <t>13,1; 26,39</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,03; 20,94</t>
+          <t>9,54; 20,96</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,02; 29,2</t>
+          <t>17,38; 29,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,4; 29,26</t>
+          <t>16,98; 29,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,24; 16,07</t>
+          <t>7,36; 15,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,41; 28,6</t>
+          <t>14,25; 26,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,72; 29,37</t>
+          <t>17,84; 29,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,1; 35,95</t>
+          <t>24,12; 36,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,6; 11,92</t>
+          <t>4,91; 11,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,91; 32,4</t>
+          <t>18,91; 33,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,64; 27,37</t>
+          <t>19,06; 27,75</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22,04; 31,06</t>
+          <t>21,99; 30,43</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,92; 12,42</t>
+          <t>6,79; 12,12</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,23; 28,21</t>
+          <t>18,65; 28,12</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,01; 17,72</t>
+          <t>8,55; 17,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,43; 11,12</t>
+          <t>4,72; 11,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,81; 14,04</t>
+          <t>6,67; 13,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,81</t>
+          <t>1,47; 6,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,28; 21,43</t>
+          <t>12,27; 21,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,71; 12,73</t>
+          <t>5,7; 12,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,28; 17,54</t>
+          <t>9,22; 17,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,44; 8,76</t>
+          <t>2,42; 8,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,68; 17,75</t>
+          <t>11,5; 17,75</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,8; 10,48</t>
+          <t>5,92; 10,51</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,09; 14,51</t>
+          <t>8,89; 14,36</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,07</t>
+          <t>2,19; 5,96</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,86; 21,77</t>
+          <t>16,86; 21,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21,05; 26,33</t>
+          <t>20,83; 26,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15,56; 20,33</t>
+          <t>15,42; 19,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,71; 18,64</t>
+          <t>12,64; 18,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,35; 24,25</t>
+          <t>19,37; 24,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,97; 30,5</t>
+          <t>24,91; 30,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,56; 19,17</t>
+          <t>14,55; 19,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,08; 18,11</t>
+          <t>13,07; 17,76</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18,85; 22,22</t>
+          <t>18,82; 22,49</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23,74; 27,66</t>
+          <t>23,84; 27,63</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15,73; 18,87</t>
+          <t>15,48; 18,75</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,75; 17,63</t>
+          <t>13,63; 17,65</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8865; 18141</t>
+          <t>8527; 18154</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12562; 23528</t>
+          <t>12277; 23426</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15634; 27286</t>
+          <t>15868; 27473</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17263; 37694</t>
+          <t>17493; 37135</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12501; 23587</t>
+          <t>12686; 24182</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22107; 35692</t>
+          <t>22185; 35643</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14942; 27920</t>
+          <t>15672; 28527</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13465; 28068</t>
+          <t>13892; 28664</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23340; 38263</t>
+          <t>24261; 39708</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36442; 54329</t>
+          <t>37825; 55557</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34734; 51920</t>
+          <t>34265; 51592</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35165; 60776</t>
+          <t>35479; 60624</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14170; 27387</t>
+          <t>13973; 26695</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25204; 39924</t>
+          <t>26108; 41639</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21428; 36069</t>
+          <t>22488; 36019</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8509; 25932</t>
+          <t>6824; 25541</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19914; 34658</t>
+          <t>19742; 34154</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31956; 47505</t>
+          <t>31791; 49242</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21375; 36010</t>
+          <t>20661; 36523</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9481; 24150</t>
+          <t>9579; 23241</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37757; 57255</t>
+          <t>37727; 56824</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62064; 84161</t>
+          <t>61599; 84485</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48225; 68401</t>
+          <t>47773; 68609</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20773; 42930</t>
+          <t>21396; 43312</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9974; 21302</t>
+          <t>10072; 21788</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15050; 27570</t>
+          <t>15369; 28157</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2875; 10880</t>
+          <t>2860; 10724</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8273; 18248</t>
+          <t>8500; 18065</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11309; 22618</t>
+          <t>11396; 22788</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17280; 29881</t>
+          <t>16540; 29575</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>739; 7356</t>
+          <t>717; 6895</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4971; 14007</t>
+          <t>4960; 13956</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23345; 39934</t>
+          <t>23665; 40165</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34788; 53389</t>
+          <t>34690; 53007</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5025; 14512</t>
+          <t>5244; 15556</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14993; 28471</t>
+          <t>15497; 29410</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10715; 22155</t>
+          <t>11143; 21968</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13158; 26258</t>
+          <t>13663; 26418</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14696; 26363</t>
+          <t>13939; 25962</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7405; 19253</t>
+          <t>6875; 18271</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12152; 23721</t>
+          <t>11429; 23629</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17457; 32060</t>
+          <t>17382; 31952</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19760; 34529</t>
+          <t>20935; 36229</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7135; 24359</t>
+          <t>7217; 24071</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25718; 42421</t>
+          <t>25348; 42777</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35135; 53639</t>
+          <t>35485; 53924</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37721; 57630</t>
+          <t>38331; 57048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17556; 38958</t>
+          <t>16474; 37146</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3192; 10186</t>
+          <t>3175; 10003</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11047; 21585</t>
+          <t>11312; 21341</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2070; 8867</t>
+          <t>1853; 8931</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>460; 5286</t>
+          <t>447; 4329</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2772; 10980</t>
+          <t>2749; 10329</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8121; 17955</t>
+          <t>7796; 17911</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4312</t>
+          <t>0; 4218</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1025; 6095</t>
+          <t>1052; 6308</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7360; 17649</t>
+          <t>7895; 17665</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22222; 36997</t>
+          <t>22068; 36373</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2993; 11061</t>
+          <t>2660; 10224</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2103; 8270</t>
+          <t>2041; 8401</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7895; 18491</t>
+          <t>7837; 18224</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11430; 22875</t>
+          <t>11179; 22318</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7440; 17553</t>
+          <t>7488; 17930</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3218; 10335</t>
+          <t>3268; 10195</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9977; 20566</t>
+          <t>9901; 20289</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15025; 27945</t>
+          <t>15272; 28228</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5084; 14274</t>
+          <t>4690; 14139</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5096; 14524</t>
+          <t>5340; 14346</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19771; 34606</t>
+          <t>20363; 35538</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28894; 47134</t>
+          <t>29721; 46498</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14980; 29062</t>
+          <t>14673; 29555</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10261; 21436</t>
+          <t>9763; 21452</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>21890; 37552</t>
+          <t>22360; 37814</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>24133; 40586</t>
+          <t>23557; 40946</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9947; 22083</t>
+          <t>10106; 21933</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17943; 35611</t>
+          <t>17736; 33552</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>24043; 39840</t>
+          <t>24199; 40366</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33507; 52152</t>
+          <t>34998; 53325</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6624; 17174</t>
+          <t>7079; 16908</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>29507; 50542</t>
+          <t>29507; 51523</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>49264; 72320</t>
+          <t>50372; 73340</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62536; 88155</t>
+          <t>62409; 86343</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19481; 34960</t>
+          <t>19096; 34125</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>51150; 79148</t>
+          <t>52326; 78888</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>14226; 27982</t>
+          <t>13498; 27640</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>7301; 18323</t>
+          <t>7777; 18692</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>11183; 23051</t>
+          <t>10950; 22869</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1612; 7645</t>
+          <t>1931; 8764</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>20144; 35154</t>
+          <t>20126; 34725</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9783; 21808</t>
+          <t>9770; 21445</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15847; 29974</t>
+          <t>15750; 29948</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3830; 13737</t>
+          <t>3788; 13267</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>37603; 57143</t>
+          <t>37010; 57146</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>19502; 35230</t>
+          <t>19888; 35300</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>30455; 48629</t>
+          <t>29793; 48096</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6663; 17493</t>
+          <t>6307; 17202</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>114820; 148284</t>
+          <t>114811; 148370</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>149607; 187162</t>
+          <t>148063; 187006</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>109625; 143203</t>
+          <t>108595; 140126</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>84455; 123880</t>
+          <t>84008; 124638</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>139843; 175288</t>
+          <t>140014; 175099</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>187350; 228833</t>
+          <t>186934; 227835</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>108303; 142659</t>
+          <t>108277; 141691</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>99644; 138030</t>
+          <t>99617; 135313</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>264539; 311881</t>
+          <t>264161; 315664</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>346823; 404113</t>
+          <t>348333; 403716</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>227897; 273282</t>
+          <t>224244; 271598</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>196171; 251523</t>
+          <t>194422; 251730</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP22_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP22_R-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29,56%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>45,44%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>33,4%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>26,39%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>24,73%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>30,75%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>36,96%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>34,86%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>29,56%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>45,44%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>33,4%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,21%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,22; 34,53</t>
+          <t>20,07; 39,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,38; 40,79</t>
+          <t>34,09; 56,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,66; 47,89</t>
+          <t>24,0; 44,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,87; 50,67</t>
+          <t>18,13; 36,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,07; 40,16</t>
+          <t>16,54; 34,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,18; 56,52</t>
+          <t>22,26; 40,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,31; 44,25</t>
+          <t>26,78; 47,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,5; 36,12</t>
+          <t>23,37; 42,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,51; 35,21</t>
+          <t>20,78; 34,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31,39; 46,11</t>
+          <t>31,8; 46,09</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,12; 42,35</t>
+          <t>28,63; 42,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,24; 39,71</t>
+          <t>23,44; 36,44</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>24,31%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>35,96%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>25,75%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11,75%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>19,88%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>31,33%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>27,9%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13,14%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>24,31%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>35,96%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>25,75%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,76; 26,28</t>
+          <t>18,21; 30,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,09; 40,01</t>
+          <t>28,79; 43,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,63; 34,65</t>
+          <t>19,47; 33,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 20,14</t>
+          <t>7,4; 18,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,15; 31,4</t>
+          <t>14,12; 26,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,6; 44,3</t>
+          <t>23,53; 39,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,73; 33,12</t>
+          <t>21,42; 35,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 18,21</t>
+          <t>10,95; 24,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,94; 27,02</t>
+          <t>18,16; 26,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,62; 39,25</t>
+          <t>28,88; 39,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22,3; 32,03</t>
+          <t>21,85; 31,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,41; 17,02</t>
+          <t>10,47; 19,24</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>23,26%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>32,12%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12,67%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>22,16%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>30,83%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>8,69%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22,13%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>23,26%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>32,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,9; 32,23</t>
+          <t>16,11; 30,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,54; 41,3</t>
+          <t>24,09; 42,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 16,05</t>
+          <t>1,06; 11,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,77; 31,39</t>
+          <t>7,29; 20,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,2; 32,4</t>
+          <t>15,25; 32,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,21; 41,51</t>
+          <t>22,7; 41,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 9,86</t>
+          <t>3,36; 16,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,38; 20,78</t>
+          <t>13,38; 30,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,16; 29,12</t>
+          <t>17,28; 29,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24,88; 38,02</t>
+          <t>25,38; 39,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 11,38</t>
+          <t>3,68; 11,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,43; 23,58</t>
+          <t>11,96; 22,58</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22,3%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29,47%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34,51%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18,68%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>20,95%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>25,54%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>25,7%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17,14%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>22,3%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,47%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34,51%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,88; 29,35</t>
+          <t>14,36; 29,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,57; 33,97</t>
+          <t>21,54; 39,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,11; 33,73</t>
+          <t>25,7; 43,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,8; 26,05</t>
+          <t>8,28; 31,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,45; 29,87</t>
+          <t>14,51; 30,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,14; 38,86</t>
+          <t>18,18; 34,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,05; 45,08</t>
+          <t>18,5; 34,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,24; 30,81</t>
+          <t>10,99; 28,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,46; 27,78</t>
+          <t>16,74; 27,64</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,18; 33,7</t>
+          <t>21,65; 33,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,36; 36,26</t>
+          <t>24,41; 36,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,11; 25,05</t>
+          <t>12,1; 26,81</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>13,74%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>26,47%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6,86%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>14,25%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>37,23%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>10,86%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>13,74%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>26,47%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,59; 23,9</t>
+          <t>6,98; 24,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,77; 48,61</t>
+          <t>17,31; 38,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,27; 20,56</t>
+          <t>0,0; 8,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 12,54</t>
+          <t>2,54; 15,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,13; 23,03</t>
+          <t>6,52; 24,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,68; 38,31</t>
+          <t>26,84; 50,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,1</t>
+          <t>4,78; 20,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 15,49</t>
+          <t>1,36; 11,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,11; 20,38</t>
+          <t>8,55; 21,13</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,34; 40,12</t>
+          <t>24,35; 39,89</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 11,39</t>
+          <t>3,29; 12,45</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,71; 11,17</t>
+          <t>2,68; 10,36</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>24,51%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>35,79%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15,81%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15,62%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>22,25%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>29,67%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>22,41%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>24,51%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>35,79%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,81%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,98; 32,51</t>
+          <t>16,82; 34,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,97; 39,86</t>
+          <t>26,59; 46,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,8; 33,04</t>
+          <t>8,08; 24,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,08; 22,08</t>
+          <t>9,0; 24,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,58; 33,97</t>
+          <t>13,95; 32,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,67; 47,44</t>
+          <t>20,32; 40,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,12; 24,49</t>
+          <t>13,9; 33,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,5; 25,53</t>
+          <t>6,9; 22,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,59; 30,69</t>
+          <t>17,05; 29,96</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25,74; 40,26</t>
+          <t>25,86; 40,96</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13,1; 26,39</t>
+          <t>13,09; 25,44</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,54; 20,96</t>
+          <t>9,86; 20,54</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>23,04%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>29,56%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7,79%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>25,83%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>22,82%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>22,74%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>10,84%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>19,71%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>23,04%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,79%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,38; 29,4</t>
+          <t>17,7; 29,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,98; 29,52</t>
+          <t>23,62; 36,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,36; 15,97</t>
+          <t>4,65; 11,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,25; 26,95</t>
+          <t>19,45; 32,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,84; 29,76</t>
+          <t>17,34; 29,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,12; 36,76</t>
+          <t>17,33; 28,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,91; 11,74</t>
+          <t>7,21; 15,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,91; 33,02</t>
+          <t>13,88; 26,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,06; 27,75</t>
+          <t>18,68; 27,11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21,99; 30,43</t>
+          <t>22,18; 30,65</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,79; 12,12</t>
+          <t>6,64; 12,16</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,65; 28,12</t>
+          <t>18,23; 27,84</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>16,29%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8,47%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>12,97%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>12,68%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>7,4%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>10,07%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>16,29%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>8,47%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,55; 17,5</t>
+          <t>11,89; 20,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,72; 11,35</t>
+          <t>5,41; 12,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,67; 13,93</t>
+          <t>8,96; 17,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,66</t>
+          <t>2,05; 8,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,27; 21,17</t>
+          <t>8,99; 17,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,7; 12,52</t>
+          <t>4,62; 11,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,22; 17,53</t>
+          <t>6,73; 14,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,42; 8,46</t>
+          <t>1,38; 5,92</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,5; 17,75</t>
+          <t>11,75; 17,76</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,92; 10,51</t>
+          <t>5,85; 10,58</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,89; 14,36</t>
+          <t>8,94; 14,52</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,96</t>
+          <t>2,28; 5,95</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>21,73%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>27,56%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>16,74%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>15,07%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>19,33%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>23,61%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>17,62%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>15,53%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>21,73%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>27,56%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>16,74%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,86; 21,79</t>
+          <t>19,2; 24,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20,83; 26,31</t>
+          <t>25,01; 30,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15,42; 19,89</t>
+          <t>14,51; 19,13</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,64; 18,75</t>
+          <t>12,93; 17,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,37; 24,23</t>
+          <t>17,06; 21,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,91; 30,36</t>
+          <t>21,26; 26,24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,55; 19,04</t>
+          <t>15,45; 19,9</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,07; 17,76</t>
+          <t>12,96; 17,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18,82; 22,49</t>
+          <t>18,8; 22,33</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23,84; 27,63</t>
+          <t>23,92; 27,66</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15,48; 18,75</t>
+          <t>15,63; 18,82</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,63; 17,65</t>
+          <t>13,28; 17,05</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17800</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28659</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>21532</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16925</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>12998</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>17657</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>21203</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25548</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>17800</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28659</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>21532</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19858</t>
+          <t>18312</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45406</t>
+          <t>35238</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8527; 18154</t>
+          <t>12088; 23984</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12277; 23426</t>
+          <t>21501; 35754</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15868; 27473</t>
+          <t>15469; 28929</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17493; 37135</t>
+          <t>11628; 23450</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12686; 24182</t>
+          <t>8693; 18356</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22185; 35643</t>
+          <t>12784; 23145</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15672; 28527</t>
+          <t>15362; 27149</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13892; 28664</t>
+          <t>13198; 24273</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24261; 39708</t>
+          <t>23434; 38390</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37825; 55557</t>
+          <t>38313; 55538</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34265; 51592</t>
+          <t>34878; 51701</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35479; 60624</t>
+          <t>28273; 43961</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>26440</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>39968</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28399</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13609</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>20189</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>32600</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>28998</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16661</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>26440</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>39968</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>28399</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15184</t>
+          <t>17098</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31846</t>
+          <t>30707</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13973; 26695</t>
+          <t>19808; 33349</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26108; 41639</t>
+          <t>32005; 48304</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22488; 36019</t>
+          <t>21475; 36674</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6824; 25541</t>
+          <t>8570; 21433</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19742; 34154</t>
+          <t>14345; 27340</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31791; 49242</t>
+          <t>24486; 41076</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20661; 36523</t>
+          <t>22268; 36757</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9579; 23241</t>
+          <t>11008; 24424</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37727; 56824</t>
+          <t>38195; 56614</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61599; 84485</t>
+          <t>62154; 84586</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47773; 68609</t>
+          <t>46810; 67481</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21396; 43312</t>
+          <t>22645; 41625</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>16361</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>22884</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7521</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>14977</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>21017</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>5811</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12736</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>16361</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>22884</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3093</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>11886</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21495</t>
+          <t>19408</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10072; 21788</t>
+          <t>11329; 21422</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15369; 28157</t>
+          <t>17162; 30003</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2860; 10724</t>
+          <t>738; 7979</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8500; 18065</t>
+          <t>4331; 12178</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11396; 22788</t>
+          <t>10310; 21720</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16540; 29575</t>
+          <t>15475; 28137</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>717; 6895</t>
+          <t>2245; 10735</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4960; 13956</t>
+          <t>7472; 16764</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23665; 40165</t>
+          <t>23840; 40285</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34690; 53007</t>
+          <t>35389; 54490</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5244; 15556</t>
+          <t>5031; 15564</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15497; 29410</t>
+          <t>13781; 26023</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17642</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24238</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27736</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>13482</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>15686</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>19860</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>19781</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12023</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17642</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>24238</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>27736</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14134</t>
+          <t>12924</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26158</t>
+          <t>26406</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11143; 21968</t>
+          <t>11357; 23565</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13663; 26418</t>
+          <t>17713; 32089</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13939; 25962</t>
+          <t>20654; 35062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6875; 18271</t>
+          <t>5975; 22968</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11429; 23629</t>
+          <t>10866; 22877</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17382; 31952</t>
+          <t>14134; 26955</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20935; 36229</t>
+          <t>14234; 26611</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7217; 24071</t>
+          <t>7789; 20077</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25348; 42777</t>
+          <t>25769; 42552</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35485; 53924</t>
+          <t>34638; 53354</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38331; 57048</t>
+          <t>38399; 56976</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16474; 37146</t>
+          <t>17303; 38341</t>
         </is>
       </c>
     </row>
@@ -2910,37 +2910,37 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>6160</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12377</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1262</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2717</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>5964</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>16346</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>4715</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1736</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6160</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>12377</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1262</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4232</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3175; 10003</t>
+          <t>3132; 10972</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11312; 21341</t>
+          <t>8091; 18149</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1853; 8931</t>
+          <t>0; 4106</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>447; 4329</t>
+          <t>1003; 6153</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2749; 10329</t>
+          <t>2728; 10141</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7796; 17911</t>
+          <t>11783; 22208</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4218</t>
+          <t>2076; 8873</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1052; 6308</t>
+          <t>484; 4069</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7895; 17665</t>
+          <t>7414; 18316</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22068; 36373</t>
+          <t>22076; 36166</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2660; 10224</t>
+          <t>2950; 11181</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2041; 8401</t>
+          <t>2012; 7789</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>14639</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>21299</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9129</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7643</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>12475</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>16612</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>12160</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6050</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>14639</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>21299</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>9129</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>9092</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15142</t>
+          <t>13596</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7837; 18224</t>
+          <t>10048; 20453</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11179; 22318</t>
+          <t>15824; 27863</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7488; 17930</t>
+          <t>4665; 14244</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3268; 10195</t>
+          <t>4406; 12224</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9901; 20289</t>
+          <t>7819; 18003</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15272; 28228</t>
+          <t>11374; 22462</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4690; 14139</t>
+          <t>7543; 18261</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5340; 14346</t>
+          <t>3157; 10227</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20363; 35538</t>
+          <t>19740; 34691</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29721; 46498</t>
+          <t>29862; 47303</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14673; 29555</t>
+          <t>14665; 28498</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9763; 21452</t>
+          <t>9337; 19449</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>31261</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>42885</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>11224</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>36517</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>29351</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>31544</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>14890</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>24540</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>31261</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>42885</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>11224</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>39640</t>
+          <t>23867</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>64180</t>
+          <t>60383</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>22360; 37814</t>
+          <t>24005; 39962</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>23557; 40946</t>
+          <t>34259; 52828</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10106; 21933</t>
+          <t>6698; 16582</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17736; 33552</t>
+          <t>27503; 46379</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>24199; 40366</t>
+          <t>22302; 37632</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34998; 53325</t>
+          <t>24034; 40047</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7079; 16908</t>
+          <t>9902; 21885</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>29507; 51523</t>
+          <t>17006; 32105</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>50372; 73340</t>
+          <t>49378; 71652</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62409; 86343</t>
+          <t>62934; 86976</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19096; 34125</t>
+          <t>18699; 34214</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>52326; 78888</t>
+          <t>48117; 73470</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>26727</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>14506</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>22152</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>7207</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>20019</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>12181</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>16526</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>3941</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>26727</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>14506</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>22152</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>7426</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>11439</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>13498; 27640</t>
+          <t>19499; 34435</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>7777; 18692</t>
+          <t>9264; 20992</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10950; 22869</t>
+          <t>15306; 29469</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1931; 8764</t>
+          <t>3262; 12942</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>20126; 34725</t>
+          <t>14198; 27057</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9770; 21445</t>
+          <t>7611; 18133</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15750; 29948</t>
+          <t>11056; 23050</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3788; 13267</t>
+          <t>1946; 8324</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>37010; 57146</t>
+          <t>37825; 57187</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>19888; 35300</t>
+          <t>19659; 35538</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>29793; 48096</t>
+          <t>29942; 48631</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6307; 17202</t>
+          <t>6827; 17852</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>243</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>194</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>149</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>157029</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>206817</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>124527</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>105622</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>131661</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>167818</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>124084</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>103235</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>157029</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>206817</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>124527</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>116838</t>
+          <t>95788</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>220073</t>
+          <t>201409</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>114811; 148370</t>
+          <t>138749; 177154</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>148063; 187006</t>
+          <t>187656; 230418</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>108595; 140126</t>
+          <t>107955; 142338</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>84008; 124638</t>
+          <t>90588; 125160</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>140014; 175099</t>
+          <t>116201; 149172</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>186934; 227835</t>
+          <t>151095; 186466</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>108277; 141691</t>
+          <t>108859; 140183</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>99617; 135313</t>
+          <t>81393; 111298</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>264161; 315664</t>
+          <t>263954; 313393</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>348333; 403716</t>
+          <t>349557; 404110</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>224244; 271598</t>
+          <t>226452; 272633</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>194422; 251730</t>
+          <t>176479; 226552</t>
         </is>
       </c>
     </row>
